--- a/prompts/financial-stuff.xlsx
+++ b/prompts/financial-stuff.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoft-my.sharepoint.com/personal/fabiopadua_microsoft_com/Documents/Git/github-copilot-levelup/prompts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoft-my.sharepoint.com/personal/fabiopadua_microsoft_com/Documents/Desktop/Level-Up - March-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{EAD9064E-1570-4000-BE5F-8AA5F42830C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB03F125-DF2E-4A36-B32C-1FAA2955600E}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{EAD9064E-1570-4000-BE5F-8AA5F42830C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F74AA005-E799-456D-9644-AE0D9053EB43}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{CEC8BA97-DFA3-40A5-AE88-7FA5E1EF965C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEC8BA97-DFA3-40A5-AE88-7FA5E1EF965C}"/>
   </bookViews>
   <sheets>
     <sheet name="January" sheetId="1" r:id="rId1"/>
@@ -2699,15 +2699,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
+      <xdr:colOff>79375</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>34925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
+      <xdr:colOff>79375</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
